--- a/12-upload_file_merge_file/output/pub_cd_map.xlsx
+++ b/12-upload_file_merge_file/output/pub_cd_map.xlsx
@@ -1,39 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\12-upload_file_merge_file\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87441041-F18D-4D5F-8A53-F8EAAF4E43FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="rem-代码映射" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+  <si>
+    <t>取数来源应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取数来源表中文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取数来源表英文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取数来源字段中文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取数来源字段英文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源代码码值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源代码码值说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标表中文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标表英文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标字段中文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标字段英文名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标代码码值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标代码说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGET_CD_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGET_CD_VAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGRT_FIELD_CN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGRT_FIELD_EN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGRT_TAB_CN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TARGRT_TAB_EN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC_CD_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC_CD_VAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC_FIELD_CN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC_FIELD_EN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC_TAB_CN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC_TAB_EN_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SRC_TAB_LIB_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>line4444444</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,85 +194,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -385,14 +498,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="4" max="14" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="22.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>111</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>111</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12-upload_file_merge_file/output/pub_cd_map.xlsx
+++ b/12-upload_file_merge_file/output/pub_cd_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\12-upload_file_merge_file\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87441041-F18D-4D5F-8A53-F8EAAF4E43FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC0EA77C-5541-4336-B7D3-491BEC3184AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="375" windowWidth="17425" windowHeight="8955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rem-代码映射" sheetId="1" r:id="rId1"/>
@@ -25,122 +25,123 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+  <si>
+    <t>SRC_TAB_LIB_NAME</t>
+  </si>
+  <si>
+    <t>SRC_TAB_EN_NAME</t>
+  </si>
+  <si>
+    <t>SRC_TAB_CN_NAME</t>
+  </si>
+  <si>
+    <t>SRC_FIELD_EN_NAME</t>
+  </si>
+  <si>
+    <t>SRC_FIELD_CN_NAME</t>
+  </si>
+  <si>
+    <t>SRC_CD_VAL</t>
+  </si>
+  <si>
+    <t>SRC_CD_DESC</t>
+  </si>
+  <si>
+    <t>TARGRT_TAB_EN_NAME</t>
+  </si>
+  <si>
+    <t>TARGRT_TAB_CN_NAME</t>
+  </si>
+  <si>
+    <t>TARGRT_FIELD_EN_NAME</t>
+  </si>
+  <si>
+    <t>TARGRT_FIELD_CN_NAME</t>
+  </si>
+  <si>
+    <t>TARGET_CD_VAL</t>
+  </si>
+  <si>
+    <t>TARGET_CD_DESC</t>
+  </si>
+  <si>
+    <t>REM</t>
+  </si>
   <si>
     <t>取数来源应用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>取数来源表中文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>取数来源表英文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>取数来源字段中文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>取数来源字段英文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>源代码码值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>源代码码值说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>目标表中文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>目标表英文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>目标字段中文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>目标字段英文名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>目标代码码值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>目标代码说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>特殊说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TARGET_CD_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TARGET_CD_VAL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TARGRT_FIELD_CN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TARGRT_FIELD_EN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TARGRT_TAB_CN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TARGRT_TAB_EN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SRC_CD_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SRC_CD_VAL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SRC_FIELD_CN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SRC_FIELD_EN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SRC_TAB_CN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SRC_TAB_EN_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SRC_TAB_LIB_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>line4444444</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LINE1111111</t>
+  </si>
+  <si>
+    <t>line1111111</t>
+  </si>
+  <si>
+    <t>line2222222</t>
+  </si>
+  <si>
+    <t>LINE2222222</t>
+  </si>
+  <si>
+    <t>line3333333</t>
+  </si>
+  <si>
+    <t>LINE3333333</t>
+  </si>
+  <si>
+    <t>line55555</t>
+  </si>
+  <si>
+    <t>LINE55555</t>
+  </si>
+  <si>
+    <t>line66666</t>
+  </si>
+  <si>
+    <t>LINE66666</t>
   </si>
 </sst>
 </file>
@@ -499,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.5546875" customWidth="1"/>
@@ -509,90 +510,90 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="22.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -680,6 +681,622 @@
         <v>2</v>
       </c>
       <c r="N4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18">
         <v>2</v>
       </c>
     </row>

--- a/12-upload_file_merge_file/output/pub_cd_map.xlsx
+++ b/12-upload_file_merge_file/output/pub_cd_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\12-upload_file_merge_file\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC0EA77C-5541-4336-B7D3-491BEC3184AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1981B2A-21D6-481F-A6BD-19D4CD53F6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="375" windowWidth="17425" windowHeight="8955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rem-代码映射" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>SRC_TAB_LIB_NAME</t>
   </si>
@@ -142,6 +142,57 @@
   </si>
   <si>
     <t>LINE66666</t>
+  </si>
+  <si>
+    <t>LINE66667</t>
+  </si>
+  <si>
+    <t>LINE66668</t>
+  </si>
+  <si>
+    <t>LINE66669</t>
+  </si>
+  <si>
+    <t>LINE66670</t>
+  </si>
+  <si>
+    <t>LINE66671</t>
+  </si>
+  <si>
+    <t>LINE66672</t>
+  </si>
+  <si>
+    <t>LINE66673</t>
+  </si>
+  <si>
+    <t>LINE66674</t>
+  </si>
+  <si>
+    <t>LINE66675</t>
+  </si>
+  <si>
+    <t>LINE66676</t>
+  </si>
+  <si>
+    <t>LINE66677</t>
+  </si>
+  <si>
+    <t>LINE66678</t>
+  </si>
+  <si>
+    <t>LINE66679</t>
+  </si>
+  <si>
+    <t>LINE66680</t>
+  </si>
+  <si>
+    <t>LINE66681</t>
+  </si>
+  <si>
+    <t>LINE66682</t>
+  </si>
+  <si>
+    <t>LINE66683</t>
   </si>
 </sst>
 </file>
@@ -500,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.5546875" customWidth="1"/>
@@ -1097,7 +1148,7 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1141,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1185,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1229,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1273,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1282,7 +1333,7 @@
         <v>37</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1297,6 +1348,710 @@
         <v>2</v>
       </c>
       <c r="N18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" t="s">
+        <v>41</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>9</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>2</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>14</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="N26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>16</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>17</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I29" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>18</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>37</v>
+      </c>
+      <c r="I30" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>19</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>20</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" t="s">
+        <v>53</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
+      <c r="N32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>2</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>22</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" t="s">
+        <v>55</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>2</v>
+      </c>
+      <c r="N34">
         <v>2</v>
       </c>
     </row>

--- a/12-upload_file_merge_file/output/pub_cd_map.xlsx
+++ b/12-upload_file_merge_file/output/pub_cd_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\12-upload_file_merge_file\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1981B2A-21D6-481F-A6BD-19D4CD53F6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B1E0B88-4854-4A31-8520-802D6495EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="81">
   <si>
     <t>SRC_TAB_LIB_NAME</t>
   </si>
@@ -132,27 +132,51 @@
     <t>LINE3333333</t>
   </si>
   <si>
+    <t>01</t>
+  </si>
+  <si>
     <t>line55555</t>
   </si>
   <si>
     <t>LINE55555</t>
   </si>
   <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
     <t>line66666</t>
   </si>
   <si>
     <t>LINE66666</t>
   </si>
   <si>
+    <t>06</t>
+  </si>
+  <si>
     <t>LINE66667</t>
   </si>
   <si>
     <t>LINE66668</t>
   </si>
   <si>
+    <t>08</t>
+  </si>
+  <si>
     <t>LINE66669</t>
   </si>
   <si>
+    <t>09</t>
+  </si>
+  <si>
     <t>LINE66670</t>
   </si>
   <si>
@@ -193,6 +217,57 @@
   </si>
   <si>
     <t>LINE66683</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>09910</t>
+  </si>
+  <si>
+    <t>00002</t>
+  </si>
+  <si>
+    <t>0544442</t>
+  </si>
+  <si>
+    <t>01111</t>
   </si>
 </sst>
 </file>
@@ -265,12 +340,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1103,17 +1180,17 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>1</v>
+      <c r="F13" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1121,7 +1198,7 @@
       <c r="K13">
         <v>2</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="4">
         <v>2</v>
       </c>
       <c r="M13">
@@ -1147,17 +1224,17 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>2</v>
+      <c r="F14" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1165,7 +1242,7 @@
       <c r="K14">
         <v>2</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="4">
         <v>2</v>
       </c>
       <c r="M14">
@@ -1191,17 +1268,17 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>3</v>
+      <c r="F15" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1209,7 +1286,7 @@
       <c r="K15">
         <v>2</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="4">
         <v>2</v>
       </c>
       <c r="M15">
@@ -1235,17 +1312,17 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>4</v>
+      <c r="F16" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1253,7 +1330,7 @@
       <c r="K16">
         <v>2</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="4">
         <v>2</v>
       </c>
       <c r="M16">
@@ -1279,17 +1356,17 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>5</v>
+      <c r="F17" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1297,7 +1374,7 @@
       <c r="K17">
         <v>2</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="4">
         <v>2</v>
       </c>
       <c r="M17">
@@ -1323,17 +1400,17 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18">
-        <v>6</v>
+      <c r="F18" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1341,7 +1418,7 @@
       <c r="K18">
         <v>2</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="4">
         <v>2</v>
       </c>
       <c r="M18">
@@ -1367,17 +1444,17 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>7</v>
+      <c r="F19" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1385,8 +1462,8 @@
       <c r="K19">
         <v>2</v>
       </c>
-      <c r="L19">
-        <v>2</v>
+      <c r="L19" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="M19">
         <v>2</v>
@@ -1411,17 +1488,17 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>8</v>
+      <c r="F20" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I20" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -1429,7 +1506,7 @@
       <c r="K20">
         <v>2</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="4">
         <v>2</v>
       </c>
       <c r="M20">
@@ -1455,17 +1532,17 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>9</v>
+      <c r="F21" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I21" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -1473,7 +1550,7 @@
       <c r="K21">
         <v>2</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="4">
         <v>2</v>
       </c>
       <c r="M21">
@@ -1499,17 +1576,17 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22">
-        <v>10</v>
+      <c r="F22" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I22" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J22">
         <v>2</v>
@@ -1517,7 +1594,7 @@
       <c r="K22">
         <v>2</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="4">
         <v>2</v>
       </c>
       <c r="M22">
@@ -1543,17 +1620,17 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>11</v>
+      <c r="F23" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -1561,7 +1638,7 @@
       <c r="K23">
         <v>2</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="4">
         <v>2</v>
       </c>
       <c r="M23">
@@ -1587,17 +1664,17 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>12</v>
+      <c r="F24" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I24" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1605,8 +1682,8 @@
       <c r="K24">
         <v>2</v>
       </c>
-      <c r="L24">
-        <v>2</v>
+      <c r="L24" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="M24">
         <v>2</v>
@@ -1631,17 +1708,17 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25">
-        <v>13</v>
+      <c r="F25" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I25" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -1649,7 +1726,7 @@
       <c r="K25">
         <v>2</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="4">
         <v>2</v>
       </c>
       <c r="M25">
@@ -1675,17 +1752,17 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>14</v>
+      <c r="F26" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I26" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -1693,7 +1770,7 @@
       <c r="K26">
         <v>2</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="4">
         <v>2</v>
       </c>
       <c r="M26">
@@ -1719,17 +1796,17 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27">
-        <v>15</v>
+      <c r="F27" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -1737,7 +1814,7 @@
       <c r="K27">
         <v>2</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="4">
         <v>2</v>
       </c>
       <c r="M27">
@@ -1763,17 +1840,17 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28">
-        <v>16</v>
+      <c r="F28" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -1781,7 +1858,7 @@
       <c r="K28">
         <v>2</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="4">
         <v>2</v>
       </c>
       <c r="M28">
@@ -1807,17 +1884,17 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29">
-        <v>17</v>
+      <c r="F29" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J29">
         <v>2</v>
@@ -1825,8 +1902,8 @@
       <c r="K29">
         <v>2</v>
       </c>
-      <c r="L29">
-        <v>2</v>
+      <c r="L29" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="M29">
         <v>2</v>
@@ -1851,17 +1928,17 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30">
-        <v>18</v>
+      <c r="F30" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -1869,7 +1946,7 @@
       <c r="K30">
         <v>2</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="4">
         <v>2</v>
       </c>
       <c r="M30">
@@ -1895,17 +1972,17 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31">
-        <v>19</v>
+      <c r="F31" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I31" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -1913,7 +1990,7 @@
       <c r="K31">
         <v>2</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="4">
         <v>2</v>
       </c>
       <c r="M31">
@@ -1939,17 +2016,17 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32">
-        <v>20</v>
+      <c r="F32" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I32" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J32">
         <v>2</v>
@@ -1957,7 +2034,7 @@
       <c r="K32">
         <v>2</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="4">
         <v>2</v>
       </c>
       <c r="M32">
@@ -1983,17 +2060,17 @@
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33">
-        <v>21</v>
+      <c r="F33" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I33" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2001,7 +2078,7 @@
       <c r="K33">
         <v>2</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="4">
         <v>2</v>
       </c>
       <c r="M33">
@@ -2027,17 +2104,17 @@
       <c r="E34">
         <v>1</v>
       </c>
-      <c r="F34">
-        <v>22</v>
+      <c r="F34" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J34">
         <v>2</v>
@@ -2045,7 +2122,7 @@
       <c r="K34">
         <v>2</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="3">
         <v>2</v>
       </c>
       <c r="M34">
